--- a/public/sample-questions.xlsx
+++ b/public/sample-questions.xlsx
@@ -31,6 +31,9 @@
     <t>Answer</t>
   </si>
   <si>
+    <t>Daily Double</t>
+  </si>
+  <si>
     <t>Geography</t>
   </si>
   <si>
@@ -124,6 +127,9 @@
     <t>Steven Spielberg</t>
   </si>
   <si>
+    <t>yes</t>
+  </si>
+  <si>
     <t>This 1994 Best Picture winner says "Life is like a box of chocolates"</t>
   </si>
   <si>
@@ -689,6 +695,18 @@
   </si>
   <si>
     <t>John Adams</t>
+  </si>
+  <si>
+    <t>Final</t>
+  </si>
+  <si>
+    <t>Seas</t>
+  </si>
+  <si>
+    <t>This sea has no coastline; it is defined by ocean currents rather than land</t>
+  </si>
+  <si>
+    <t>The Sargasso Sea</t>
   </si>
 </sst>
 </file>
@@ -733,6 +751,7 @@
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="70" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -751,22 +770,25 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2">
         <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -774,16 +796,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3">
         <v>200</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -791,16 +813,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4">
         <v>300</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -808,16 +830,16 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5">
         <v>400</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -825,16 +847,16 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6">
         <v>500</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -842,16 +864,16 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7">
         <v>100</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -859,16 +881,16 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8">
         <v>200</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
@@ -876,16 +898,16 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9">
         <v>300</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
@@ -893,16 +915,16 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10">
         <v>400</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
@@ -910,16 +932,16 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11">
         <v>500</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12">
@@ -927,16 +949,16 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C12">
         <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
@@ -944,16 +966,16 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C13">
         <v>200</v>
       </c>
       <c r="D13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -961,16 +983,16 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C14">
         <v>300</v>
       </c>
       <c r="D14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15">
@@ -978,16 +1000,19 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C15">
         <v>400</v>
       </c>
       <c r="D15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E15" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="F15" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="16">
@@ -995,16 +1020,16 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C16">
         <v>500</v>
       </c>
       <c r="D16" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E16" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17">
@@ -1012,16 +1037,16 @@
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C17">
         <v>100</v>
       </c>
       <c r="D17" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18">
@@ -1029,16 +1054,16 @@
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C18">
         <v>200</v>
       </c>
       <c r="D18" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E18" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19">
@@ -1046,16 +1071,16 @@
         <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C19">
         <v>300</v>
       </c>
       <c r="D19" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E19" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20">
@@ -1063,16 +1088,16 @@
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C20">
         <v>400</v>
       </c>
       <c r="D20" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E20" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21">
@@ -1080,16 +1105,16 @@
         <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C21">
         <v>500</v>
       </c>
       <c r="D21" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E21" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22">
@@ -1097,16 +1122,16 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C22">
         <v>100</v>
       </c>
       <c r="D22" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E22" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23">
@@ -1114,16 +1139,16 @@
         <v>1</v>
       </c>
       <c r="B23" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C23">
         <v>200</v>
       </c>
       <c r="D23" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E23" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24">
@@ -1131,16 +1156,16 @@
         <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C24">
         <v>300</v>
       </c>
       <c r="D24" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E24" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25">
@@ -1148,16 +1173,16 @@
         <v>1</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C25">
         <v>400</v>
       </c>
       <c r="D25" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E25" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26">
@@ -1165,16 +1190,16 @@
         <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C26">
         <v>500</v>
       </c>
       <c r="D26" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E26" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27">
@@ -1182,16 +1207,16 @@
         <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C27">
         <v>200</v>
       </c>
       <c r="D27" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E27" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28">
@@ -1199,16 +1224,16 @@
         <v>2</v>
       </c>
       <c r="B28" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C28">
         <v>400</v>
       </c>
       <c r="D28" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E28" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29">
@@ -1216,16 +1241,16 @@
         <v>2</v>
       </c>
       <c r="B29" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C29">
         <v>600</v>
       </c>
       <c r="D29" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E29" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30">
@@ -1233,16 +1258,16 @@
         <v>2</v>
       </c>
       <c r="B30" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C30">
         <v>800</v>
       </c>
       <c r="D30" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E30" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31">
@@ -1250,16 +1275,16 @@
         <v>2</v>
       </c>
       <c r="B31" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C31">
         <v>1000</v>
       </c>
       <c r="D31" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E31" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32">
@@ -1267,16 +1292,16 @@
         <v>2</v>
       </c>
       <c r="B32" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C32">
         <v>200</v>
       </c>
       <c r="D32" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E32" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33">
@@ -1284,16 +1309,16 @@
         <v>2</v>
       </c>
       <c r="B33" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C33">
         <v>400</v>
       </c>
       <c r="D33" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E33" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34">
@@ -1301,16 +1326,16 @@
         <v>2</v>
       </c>
       <c r="B34" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C34">
         <v>600</v>
       </c>
       <c r="D34" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E34" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35">
@@ -1318,16 +1343,16 @@
         <v>2</v>
       </c>
       <c r="B35" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C35">
         <v>800</v>
       </c>
       <c r="D35" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E35" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36">
@@ -1335,16 +1360,16 @@
         <v>2</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C36">
         <v>1000</v>
       </c>
       <c r="D36" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E36" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37">
@@ -1352,16 +1377,16 @@
         <v>2</v>
       </c>
       <c r="B37" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C37">
         <v>200</v>
       </c>
       <c r="D37" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E37" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="38">
@@ -1369,16 +1394,16 @@
         <v>2</v>
       </c>
       <c r="B38" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C38">
         <v>400</v>
       </c>
       <c r="D38" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E38" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="39">
@@ -1386,16 +1411,16 @@
         <v>2</v>
       </c>
       <c r="B39" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C39">
         <v>600</v>
       </c>
       <c r="D39" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E39" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="40">
@@ -1403,16 +1428,19 @@
         <v>2</v>
       </c>
       <c r="B40" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C40">
         <v>800</v>
       </c>
       <c r="D40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E40" t="s">
-        <v>90</v>
+        <v>92</v>
+      </c>
+      <c r="F40" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="41">
@@ -1420,16 +1448,16 @@
         <v>2</v>
       </c>
       <c r="B41" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C41">
         <v>1000</v>
       </c>
       <c r="D41" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E41" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="42">
@@ -1437,16 +1465,16 @@
         <v>2</v>
       </c>
       <c r="B42" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C42">
         <v>200</v>
       </c>
       <c r="D42" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E42" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="43">
@@ -1454,16 +1482,16 @@
         <v>2</v>
       </c>
       <c r="B43" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C43">
         <v>400</v>
       </c>
       <c r="D43" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E43" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="44">
@@ -1471,16 +1499,16 @@
         <v>2</v>
       </c>
       <c r="B44" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C44">
         <v>600</v>
       </c>
       <c r="D44" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E44" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="45">
@@ -1488,16 +1516,16 @@
         <v>2</v>
       </c>
       <c r="B45" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C45">
         <v>800</v>
       </c>
       <c r="D45" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E45" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="46">
@@ -1505,16 +1533,16 @@
         <v>2</v>
       </c>
       <c r="B46" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C46">
         <v>1000</v>
       </c>
       <c r="D46" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E46" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="47">
@@ -1522,16 +1550,16 @@
         <v>2</v>
       </c>
       <c r="B47" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C47">
         <v>200</v>
       </c>
       <c r="D47" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E47" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="48">
@@ -1539,16 +1567,16 @@
         <v>2</v>
       </c>
       <c r="B48" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C48">
         <v>400</v>
       </c>
       <c r="D48" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E48" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="49">
@@ -1556,16 +1584,16 @@
         <v>2</v>
       </c>
       <c r="B49" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C49">
         <v>600</v>
       </c>
       <c r="D49" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E49" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="50">
@@ -1573,16 +1601,16 @@
         <v>2</v>
       </c>
       <c r="B50" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C50">
         <v>800</v>
       </c>
       <c r="D50" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E50" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="51">
@@ -1590,16 +1618,19 @@
         <v>2</v>
       </c>
       <c r="B51" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C51">
         <v>1000</v>
       </c>
       <c r="D51" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E51" t="s">
-        <v>114</v>
+        <v>116</v>
+      </c>
+      <c r="F51" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="52">
@@ -1607,16 +1638,16 @@
         <v>3</v>
       </c>
       <c r="B52" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C52">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="D52" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E52" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="53">
@@ -1624,16 +1655,16 @@
         <v>3</v>
       </c>
       <c r="B53" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C53">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="D53" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E53" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="54">
@@ -1641,16 +1672,16 @@
         <v>3</v>
       </c>
       <c r="B54" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C54">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="D54" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E54" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="55">
@@ -1658,16 +1689,16 @@
         <v>3</v>
       </c>
       <c r="B55" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C55">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="D55" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E55" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="56">
@@ -1675,16 +1706,16 @@
         <v>3</v>
       </c>
       <c r="B56" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C56">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="D56" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E56" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="57">
@@ -1692,16 +1723,16 @@
         <v>3</v>
       </c>
       <c r="B57" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C57">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="D57" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E57" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="58">
@@ -1709,16 +1740,16 @@
         <v>3</v>
       </c>
       <c r="B58" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C58">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="D58" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E58" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="59">
@@ -1726,16 +1757,16 @@
         <v>3</v>
       </c>
       <c r="B59" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C59">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="D59" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E59" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="60">
@@ -1743,16 +1774,16 @@
         <v>3</v>
       </c>
       <c r="B60" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C60">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="D60" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E60" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="61">
@@ -1760,16 +1791,16 @@
         <v>3</v>
       </c>
       <c r="B61" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C61">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="D61" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E61" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="62">
@@ -1777,16 +1808,16 @@
         <v>3</v>
       </c>
       <c r="B62" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C62">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="D62" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E62" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="63">
@@ -1794,16 +1825,16 @@
         <v>3</v>
       </c>
       <c r="B63" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C63">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="D63" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E63" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="64">
@@ -1811,16 +1842,16 @@
         <v>3</v>
       </c>
       <c r="B64" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C64">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="D64" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E64" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="65">
@@ -1828,16 +1859,19 @@
         <v>3</v>
       </c>
       <c r="B65" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C65">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="D65" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E65" t="s">
-        <v>145</v>
+        <v>147</v>
+      </c>
+      <c r="F65" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="66">
@@ -1845,16 +1879,16 @@
         <v>3</v>
       </c>
       <c r="B66" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C66">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="D66" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E66" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="67">
@@ -1862,16 +1896,16 @@
         <v>3</v>
       </c>
       <c r="B67" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C67">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="D67" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E67" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="68">
@@ -1879,16 +1913,16 @@
         <v>3</v>
       </c>
       <c r="B68" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C68">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="D68" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E68" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="69">
@@ -1896,16 +1930,16 @@
         <v>3</v>
       </c>
       <c r="B69" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C69">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="D69" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E69" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="70">
@@ -1913,16 +1947,16 @@
         <v>3</v>
       </c>
       <c r="B70" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C70">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="D70" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E70" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="71">
@@ -1930,16 +1964,16 @@
         <v>3</v>
       </c>
       <c r="B71" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C71">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="D71" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E71" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="72">
@@ -1947,16 +1981,16 @@
         <v>3</v>
       </c>
       <c r="B72" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C72">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="D72" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E72" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="73">
@@ -1964,16 +1998,16 @@
         <v>3</v>
       </c>
       <c r="B73" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C73">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="D73" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E73" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="74">
@@ -1981,16 +2015,16 @@
         <v>3</v>
       </c>
       <c r="B74" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C74">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="D74" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E74" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="75">
@@ -1998,16 +2032,16 @@
         <v>3</v>
       </c>
       <c r="B75" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C75">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="D75" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E75" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="76">
@@ -2015,16 +2049,16 @@
         <v>3</v>
       </c>
       <c r="B76" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C76">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="D76" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E76" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="77">
@@ -2032,16 +2066,16 @@
         <v>4</v>
       </c>
       <c r="B77" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C77">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="D77" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E77" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="78">
@@ -2049,16 +2083,16 @@
         <v>4</v>
       </c>
       <c r="B78" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C78">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="D78" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E78" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="79">
@@ -2066,16 +2100,16 @@
         <v>4</v>
       </c>
       <c r="B79" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C79">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="D79" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E79" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="80">
@@ -2083,16 +2117,16 @@
         <v>4</v>
       </c>
       <c r="B80" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C80">
-        <v>1600</v>
+        <v>800</v>
       </c>
       <c r="D80" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E80" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="81">
@@ -2100,16 +2134,16 @@
         <v>4</v>
       </c>
       <c r="B81" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C81">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="D81" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E81" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="82">
@@ -2117,16 +2151,16 @@
         <v>4</v>
       </c>
       <c r="B82" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C82">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="D82" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E82" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="83">
@@ -2134,16 +2168,16 @@
         <v>4</v>
       </c>
       <c r="B83" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C83">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="D83" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E83" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="84">
@@ -2151,16 +2185,16 @@
         <v>4</v>
       </c>
       <c r="B84" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C84">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="D84" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E84" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="85">
@@ -2168,16 +2202,16 @@
         <v>4</v>
       </c>
       <c r="B85" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C85">
-        <v>1600</v>
+        <v>800</v>
       </c>
       <c r="D85" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E85" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="86">
@@ -2185,16 +2219,19 @@
         <v>4</v>
       </c>
       <c r="B86" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C86">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="D86" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E86" t="s">
-        <v>191</v>
+        <v>193</v>
+      </c>
+      <c r="F86" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="87">
@@ -2202,16 +2239,16 @@
         <v>4</v>
       </c>
       <c r="B87" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C87">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="D87" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E87" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="88">
@@ -2219,16 +2256,16 @@
         <v>4</v>
       </c>
       <c r="B88" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C88">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="D88" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E88" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="89">
@@ -2236,16 +2273,16 @@
         <v>4</v>
       </c>
       <c r="B89" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C89">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="D89" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E89" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="90">
@@ -2253,16 +2290,19 @@
         <v>4</v>
       </c>
       <c r="B90" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C90">
-        <v>1600</v>
+        <v>800</v>
       </c>
       <c r="D90" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E90" t="s">
-        <v>200</v>
+        <v>202</v>
+      </c>
+      <c r="F90" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="91">
@@ -2270,16 +2310,16 @@
         <v>4</v>
       </c>
       <c r="B91" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C91">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="D91" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E91" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="92">
@@ -2287,16 +2327,16 @@
         <v>4</v>
       </c>
       <c r="B92" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C92">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="D92" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E92" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="93">
@@ -2304,16 +2344,16 @@
         <v>4</v>
       </c>
       <c r="B93" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C93">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="D93" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E93" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="94">
@@ -2321,16 +2361,16 @@
         <v>4</v>
       </c>
       <c r="B94" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C94">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="D94" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E94" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="95">
@@ -2338,16 +2378,16 @@
         <v>4</v>
       </c>
       <c r="B95" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C95">
-        <v>1600</v>
+        <v>800</v>
       </c>
       <c r="D95" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E95" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="96">
@@ -2355,16 +2395,16 @@
         <v>4</v>
       </c>
       <c r="B96" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C96">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="D96" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E96" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="97">
@@ -2372,16 +2412,16 @@
         <v>4</v>
       </c>
       <c r="B97" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C97">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="D97" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E97" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="98">
@@ -2389,16 +2429,16 @@
         <v>4</v>
       </c>
       <c r="B98" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C98">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="D98" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E98" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="99">
@@ -2406,16 +2446,16 @@
         <v>4</v>
       </c>
       <c r="B99" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C99">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="D99" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E99" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="100">
@@ -2423,16 +2463,16 @@
         <v>4</v>
       </c>
       <c r="B100" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C100">
-        <v>1600</v>
+        <v>800</v>
       </c>
       <c r="D100" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E100" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="101">
@@ -2440,16 +2480,30 @@
         <v>4</v>
       </c>
       <c r="B101" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C101">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="D101" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E101" t="s">
-        <v>224</v>
+        <v>226</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>227</v>
+      </c>
+      <c r="B102" t="s">
+        <v>228</v>
+      </c>
+      <c r="D102" t="s">
+        <v>229</v>
+      </c>
+      <c r="E102" t="s">
+        <v>230</v>
       </c>
     </row>
   </sheetData>

--- a/public/sample-questions.xlsx
+++ b/public/sample-questions.xlsx
@@ -202,6 +202,39 @@
     <t>Three</t>
   </si>
   <si>
+    <t>Music</t>
+  </si>
+  <si>
+    <t>A standard guitar has this many strings</t>
+  </si>
+  <si>
+    <t>Six</t>
+  </si>
+  <si>
+    <t>The "King of Pop"</t>
+  </si>
+  <si>
+    <t>Michael Jackson</t>
+  </si>
+  <si>
+    <t>The band of John Lennon and Paul McCartney</t>
+  </si>
+  <si>
+    <t>The Beatles</t>
+  </si>
+  <si>
+    <t>Queen's 1975 rock-opera single</t>
+  </si>
+  <si>
+    <t>Bohemian Rhapsody</t>
+  </si>
+  <si>
+    <t>This composer wrote his Ninth Symphony while almost completely deaf</t>
+  </si>
+  <si>
+    <t>Ludwig van Beethoven</t>
+  </si>
+  <si>
     <t>US History</t>
   </si>
   <si>
@@ -235,39 +268,6 @@
     <t>The 13th Amendment</t>
   </si>
   <si>
-    <t>Music</t>
-  </si>
-  <si>
-    <t>A standard guitar has this many strings</t>
-  </si>
-  <si>
-    <t>Six</t>
-  </si>
-  <si>
-    <t>The "King of Pop"</t>
-  </si>
-  <si>
-    <t>Michael Jackson</t>
-  </si>
-  <si>
-    <t>The band of John Lennon and Paul McCartney</t>
-  </si>
-  <si>
-    <t>The Beatles</t>
-  </si>
-  <si>
-    <t>Queen's 1975 rock-opera single</t>
-  </si>
-  <si>
-    <t>Bohemian Rhapsody</t>
-  </si>
-  <si>
-    <t>This composer wrote his Ninth Symphony while almost completely deaf</t>
-  </si>
-  <si>
-    <t>Ludwig van Beethoven</t>
-  </si>
-  <si>
     <t>Literature</t>
   </si>
   <si>
@@ -301,39 +301,6 @@
     <t>1984</t>
   </si>
   <si>
-    <t>Sports</t>
-  </si>
-  <si>
-    <t>The sport played at Wimbledon</t>
-  </si>
-  <si>
-    <t>Tennis</t>
-  </si>
-  <si>
-    <t>A soccer team has this many players on the field</t>
-  </si>
-  <si>
-    <t>Eleven</t>
-  </si>
-  <si>
-    <t>The Olympic flag has this many rings</t>
-  </si>
-  <si>
-    <t>Five</t>
-  </si>
-  <si>
-    <t>The ancient Olympic Games originated in this country</t>
-  </si>
-  <si>
-    <t>Greece</t>
-  </si>
-  <si>
-    <t>The winner of the 2022 FIFA World Cup</t>
-  </si>
-  <si>
-    <t>Argentina</t>
-  </si>
-  <si>
     <t>Space</t>
   </si>
   <si>
@@ -367,103 +334,70 @@
     <t>1969</t>
   </si>
   <si>
-    <t>World Capitals</t>
-  </si>
-  <si>
-    <t>France</t>
-  </si>
-  <si>
-    <t>Paris</t>
-  </si>
-  <si>
-    <t>Japan</t>
-  </si>
-  <si>
-    <t>Tokyo</t>
-  </si>
-  <si>
-    <t>Canada</t>
-  </si>
-  <si>
-    <t>Ottawa</t>
-  </si>
-  <si>
-    <t>Australia</t>
-  </si>
-  <si>
-    <t>Canberra</t>
-  </si>
-  <si>
-    <t>Brazil</t>
-  </si>
-  <si>
-    <t>Brasília</t>
-  </si>
-  <si>
-    <t>Human Body</t>
-  </si>
-  <si>
-    <t>The organ that pumps blood around the body</t>
-  </si>
-  <si>
-    <t>The heart</t>
-  </si>
-  <si>
-    <t>The largest organ of the human body</t>
-  </si>
-  <si>
-    <t>The skin</t>
-  </si>
-  <si>
-    <t>Your skin makes this vitamin when exposed to sunlight</t>
-  </si>
-  <si>
-    <t>Vitamin D</t>
-  </si>
-  <si>
-    <t>An adult human has this many bones</t>
-  </si>
-  <si>
-    <t>206</t>
-  </si>
-  <si>
-    <t>The smallest bone in the body, found in the ear</t>
-  </si>
-  <si>
-    <t>The stapes</t>
-  </si>
-  <si>
-    <t>TV</t>
-  </si>
-  <si>
-    <t>The yellow-skinned family from Springfield</t>
-  </si>
-  <si>
-    <t>The Simpsons</t>
-  </si>
-  <si>
-    <t>Sitcom about Ross, Rachel, Monica, Chandler, Joey and Phoebe</t>
-  </si>
-  <si>
-    <t>Friends</t>
-  </si>
-  <si>
-    <t>Fantasy series about the fight for the Iron Throne</t>
-  </si>
-  <si>
-    <t>Game of Thrones</t>
-  </si>
-  <si>
-    <t>Chemistry teacher Walter White stars in this series</t>
-  </si>
-  <si>
-    <t>Breaking Bad</t>
-  </si>
-  <si>
-    <t>Korean series where contestants in green tracksuits play deadly games</t>
-  </si>
-  <si>
-    <t>Squid Game</t>
+    <t>Mythology</t>
+  </si>
+  <si>
+    <t>The king of the Greek gods</t>
+  </si>
+  <si>
+    <t>Zeus</t>
+  </si>
+  <si>
+    <t>The Norse god of thunder</t>
+  </si>
+  <si>
+    <t>Thor</t>
+  </si>
+  <si>
+    <t>The Roman name for the Greek god Poseidon</t>
+  </si>
+  <si>
+    <t>Neptune</t>
+  </si>
+  <si>
+    <t>The jackal-headed Egyptian god of embalming</t>
+  </si>
+  <si>
+    <t>Anubis</t>
+  </si>
+  <si>
+    <t>The hero who slew Medusa</t>
+  </si>
+  <si>
+    <t>Perseus</t>
+  </si>
+  <si>
+    <t>Art</t>
+  </si>
+  <si>
+    <t>He painted the Mona Lisa</t>
+  </si>
+  <si>
+    <t>Leonardo da Vinci</t>
+  </si>
+  <si>
+    <t>He painted The Starry Night</t>
+  </si>
+  <si>
+    <t>Vincent van Gogh</t>
+  </si>
+  <si>
+    <t>The Paris museum that houses the Mona Lisa</t>
+  </si>
+  <si>
+    <t>The Louvre</t>
+  </si>
+  <si>
+    <t>The Spanish artist who co-founded Cubism</t>
+  </si>
+  <si>
+    <t>Pablo Picasso</t>
+  </si>
+  <si>
+    <t>Michelangelo painted the ceiling of this chapel</t>
+  </si>
+  <si>
+    <t>The Sistine Chapel</t>
   </si>
   <si>
     <t>Inventions</t>
@@ -497,204 +431,6 @@
   </si>
   <si>
     <t>Kitty Hawk</t>
-  </si>
-  <si>
-    <t>Mythology</t>
-  </si>
-  <si>
-    <t>The king of the Greek gods</t>
-  </si>
-  <si>
-    <t>Zeus</t>
-  </si>
-  <si>
-    <t>The Norse god of thunder</t>
-  </si>
-  <si>
-    <t>Thor</t>
-  </si>
-  <si>
-    <t>The Roman name for the Greek god Poseidon</t>
-  </si>
-  <si>
-    <t>Neptune</t>
-  </si>
-  <si>
-    <t>The jackal-headed Egyptian god of embalming</t>
-  </si>
-  <si>
-    <t>Anubis</t>
-  </si>
-  <si>
-    <t>The hero who slew Medusa</t>
-  </si>
-  <si>
-    <t>Perseus</t>
-  </si>
-  <si>
-    <t>Languages</t>
-  </si>
-  <si>
-    <t>"Hola" means hello in this language</t>
-  </si>
-  <si>
-    <t>Spanish</t>
-  </si>
-  <si>
-    <t>"Danke" means thank you in this language</t>
-  </si>
-  <si>
-    <t>German</t>
-  </si>
-  <si>
-    <t>The language of ancient Rome</t>
-  </si>
-  <si>
-    <t>Latin</t>
-  </si>
-  <si>
-    <t>The script used to write Russian</t>
-  </si>
-  <si>
-    <t>Cyrillic</t>
-  </si>
-  <si>
-    <t>The most spoken native language in the world</t>
-  </si>
-  <si>
-    <t>Mandarin Chinese</t>
-  </si>
-  <si>
-    <t>Math</t>
-  </si>
-  <si>
-    <t>7 x 8</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>The square root of 144</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>Pi to two decimal places</t>
-  </si>
-  <si>
-    <t>3.14</t>
-  </si>
-  <si>
-    <t>The interior angles of a triangle add up to this many degrees</t>
-  </si>
-  <si>
-    <t>180</t>
-  </si>
-  <si>
-    <t>The name for the number 1 followed by 100 zeros</t>
-  </si>
-  <si>
-    <t>A googol</t>
-  </si>
-  <si>
-    <t>Art</t>
-  </si>
-  <si>
-    <t>He painted the Mona Lisa</t>
-  </si>
-  <si>
-    <t>Leonardo da Vinci</t>
-  </si>
-  <si>
-    <t>He painted The Starry Night</t>
-  </si>
-  <si>
-    <t>Vincent van Gogh</t>
-  </si>
-  <si>
-    <t>The Paris museum that houses the Mona Lisa</t>
-  </si>
-  <si>
-    <t>The Louvre</t>
-  </si>
-  <si>
-    <t>The Spanish artist who co-founded Cubism</t>
-  </si>
-  <si>
-    <t>Pablo Picasso</t>
-  </si>
-  <si>
-    <t>Michelangelo painted the ceiling of this chapel</t>
-  </si>
-  <si>
-    <t>The Sistine Chapel</t>
-  </si>
-  <si>
-    <t>Tech</t>
-  </si>
-  <si>
-    <t>The company that makes the iPhone</t>
-  </si>
-  <si>
-    <t>Apple</t>
-  </si>
-  <si>
-    <t>He co-founded Microsoft with Paul Allen</t>
-  </si>
-  <si>
-    <t>Bill Gates</t>
-  </si>
-  <si>
-    <t>CPU stands for this</t>
-  </si>
-  <si>
-    <t>Central Processing Unit</t>
-  </si>
-  <si>
-    <t>Binary digits, 0 and 1, are called this</t>
-  </si>
-  <si>
-    <t>Bits</t>
-  </si>
-  <si>
-    <t>Linus Torvalds created this open-source operating system kernel</t>
-  </si>
-  <si>
-    <t>Linux</t>
-  </si>
-  <si>
-    <t>Famous Firsts</t>
-  </si>
-  <si>
-    <t>The first woman to fly solo across the Atlantic</t>
-  </si>
-  <si>
-    <t>Amelia Earhart</t>
-  </si>
-  <si>
-    <t>The first artificial satellite, launched in 1957</t>
-  </si>
-  <si>
-    <t>Sputnik</t>
-  </si>
-  <si>
-    <t>The first woman to win a Nobel Prize</t>
-  </si>
-  <si>
-    <t>Marie Curie</t>
-  </si>
-  <si>
-    <t>He led the first expedition to reach the South Pole in 1911</t>
-  </si>
-  <si>
-    <t>Roald Amundsen</t>
-  </si>
-  <si>
-    <t>The first US president to live in the White House</t>
-  </si>
-  <si>
-    <t>John Adams</t>
   </si>
   <si>
     <t>Final</t>
@@ -1204,13 +940,13 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B27" t="s">
         <v>62</v>
       </c>
       <c r="C27">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="D27" t="s">
         <v>63</v>
@@ -1221,13 +957,13 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B28" t="s">
         <v>62</v>
       </c>
       <c r="C28">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="D28" t="s">
         <v>65</v>
@@ -1238,13 +974,13 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B29" t="s">
         <v>62</v>
       </c>
       <c r="C29">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="D29" t="s">
         <v>67</v>
@@ -1255,13 +991,13 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B30" t="s">
         <v>62</v>
       </c>
       <c r="C30">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="D30" t="s">
         <v>69</v>
@@ -1272,13 +1008,13 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B31" t="s">
         <v>62</v>
       </c>
       <c r="C31">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="D31" t="s">
         <v>71</v>
@@ -1544,6 +1280,9 @@
       <c r="E46" t="s">
         <v>105</v>
       </c>
+      <c r="F46" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47">
@@ -1629,19 +1368,16 @@
       <c r="E51" t="s">
         <v>116</v>
       </c>
-      <c r="F51" t="s">
-        <v>37</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B52" t="s">
         <v>117</v>
       </c>
       <c r="C52">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="D52" t="s">
         <v>118</v>
@@ -1652,13 +1388,13 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B53" t="s">
         <v>117</v>
       </c>
       <c r="C53">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="D53" t="s">
         <v>120</v>
@@ -1669,13 +1405,13 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B54" t="s">
         <v>117</v>
       </c>
       <c r="C54">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="D54" t="s">
         <v>122</v>
@@ -1686,13 +1422,13 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B55" t="s">
         <v>117</v>
       </c>
       <c r="C55">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="D55" t="s">
         <v>124</v>
@@ -1703,13 +1439,13 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B56" t="s">
         <v>117</v>
       </c>
       <c r="C56">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="D56" t="s">
         <v>126</v>
@@ -1720,13 +1456,13 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B57" t="s">
         <v>128</v>
       </c>
       <c r="C57">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="D57" t="s">
         <v>129</v>
@@ -1737,13 +1473,13 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B58" t="s">
         <v>128</v>
       </c>
       <c r="C58">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="D58" t="s">
         <v>131</v>
@@ -1754,13 +1490,13 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B59" t="s">
         <v>128</v>
       </c>
       <c r="C59">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="D59" t="s">
         <v>133</v>
@@ -1771,13 +1507,13 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B60" t="s">
         <v>128</v>
       </c>
       <c r="C60">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="D60" t="s">
         <v>135</v>
@@ -1788,13 +1524,13 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B61" t="s">
         <v>128</v>
       </c>
       <c r="C61">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="D61" t="s">
         <v>137</v>
@@ -1804,706 +1540,17 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62">
-        <v>3</v>
+      <c r="A62" t="s">
+        <v>139</v>
       </c>
       <c r="B62" t="s">
-        <v>139</v>
-      </c>
-      <c r="C62">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="D62" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E62" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63">
-        <v>3</v>
-      </c>
-      <c r="B63" t="s">
-        <v>139</v>
-      </c>
-      <c r="C63">
-        <v>200</v>
-      </c>
-      <c r="D63" t="s">
         <v>142</v>
-      </c>
-      <c r="E63" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64">
-        <v>3</v>
-      </c>
-      <c r="B64" t="s">
-        <v>139</v>
-      </c>
-      <c r="C64">
-        <v>300</v>
-      </c>
-      <c r="D64" t="s">
-        <v>144</v>
-      </c>
-      <c r="E64" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65">
-        <v>3</v>
-      </c>
-      <c r="B65" t="s">
-        <v>139</v>
-      </c>
-      <c r="C65">
-        <v>400</v>
-      </c>
-      <c r="D65" t="s">
-        <v>146</v>
-      </c>
-      <c r="E65" t="s">
-        <v>147</v>
-      </c>
-      <c r="F65" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66">
-        <v>3</v>
-      </c>
-      <c r="B66" t="s">
-        <v>139</v>
-      </c>
-      <c r="C66">
-        <v>500</v>
-      </c>
-      <c r="D66" t="s">
-        <v>148</v>
-      </c>
-      <c r="E66" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67">
-        <v>3</v>
-      </c>
-      <c r="B67" t="s">
-        <v>150</v>
-      </c>
-      <c r="C67">
-        <v>100</v>
-      </c>
-      <c r="D67" t="s">
-        <v>151</v>
-      </c>
-      <c r="E67" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68">
-        <v>3</v>
-      </c>
-      <c r="B68" t="s">
-        <v>150</v>
-      </c>
-      <c r="C68">
-        <v>200</v>
-      </c>
-      <c r="D68" t="s">
-        <v>153</v>
-      </c>
-      <c r="E68" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69">
-        <v>3</v>
-      </c>
-      <c r="B69" t="s">
-        <v>150</v>
-      </c>
-      <c r="C69">
-        <v>300</v>
-      </c>
-      <c r="D69" t="s">
-        <v>155</v>
-      </c>
-      <c r="E69" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70">
-        <v>3</v>
-      </c>
-      <c r="B70" t="s">
-        <v>150</v>
-      </c>
-      <c r="C70">
-        <v>400</v>
-      </c>
-      <c r="D70" t="s">
-        <v>157</v>
-      </c>
-      <c r="E70" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71">
-        <v>3</v>
-      </c>
-      <c r="B71" t="s">
-        <v>150</v>
-      </c>
-      <c r="C71">
-        <v>500</v>
-      </c>
-      <c r="D71" t="s">
-        <v>159</v>
-      </c>
-      <c r="E71" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72">
-        <v>3</v>
-      </c>
-      <c r="B72" t="s">
-        <v>161</v>
-      </c>
-      <c r="C72">
-        <v>100</v>
-      </c>
-      <c r="D72" t="s">
-        <v>162</v>
-      </c>
-      <c r="E72" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73">
-        <v>3</v>
-      </c>
-      <c r="B73" t="s">
-        <v>161</v>
-      </c>
-      <c r="C73">
-        <v>200</v>
-      </c>
-      <c r="D73" t="s">
-        <v>164</v>
-      </c>
-      <c r="E73" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74">
-        <v>3</v>
-      </c>
-      <c r="B74" t="s">
-        <v>161</v>
-      </c>
-      <c r="C74">
-        <v>300</v>
-      </c>
-      <c r="D74" t="s">
-        <v>166</v>
-      </c>
-      <c r="E74" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75">
-        <v>3</v>
-      </c>
-      <c r="B75" t="s">
-        <v>161</v>
-      </c>
-      <c r="C75">
-        <v>400</v>
-      </c>
-      <c r="D75" t="s">
-        <v>168</v>
-      </c>
-      <c r="E75" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76">
-        <v>3</v>
-      </c>
-      <c r="B76" t="s">
-        <v>161</v>
-      </c>
-      <c r="C76">
-        <v>500</v>
-      </c>
-      <c r="D76" t="s">
-        <v>170</v>
-      </c>
-      <c r="E76" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77">
-        <v>4</v>
-      </c>
-      <c r="B77" t="s">
-        <v>172</v>
-      </c>
-      <c r="C77">
-        <v>200</v>
-      </c>
-      <c r="D77" t="s">
-        <v>173</v>
-      </c>
-      <c r="E77" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78">
-        <v>4</v>
-      </c>
-      <c r="B78" t="s">
-        <v>172</v>
-      </c>
-      <c r="C78">
-        <v>400</v>
-      </c>
-      <c r="D78" t="s">
-        <v>175</v>
-      </c>
-      <c r="E78" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79">
-        <v>4</v>
-      </c>
-      <c r="B79" t="s">
-        <v>172</v>
-      </c>
-      <c r="C79">
-        <v>600</v>
-      </c>
-      <c r="D79" t="s">
-        <v>177</v>
-      </c>
-      <c r="E79" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80">
-        <v>4</v>
-      </c>
-      <c r="B80" t="s">
-        <v>172</v>
-      </c>
-      <c r="C80">
-        <v>800</v>
-      </c>
-      <c r="D80" t="s">
-        <v>179</v>
-      </c>
-      <c r="E80" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81">
-        <v>4</v>
-      </c>
-      <c r="B81" t="s">
-        <v>172</v>
-      </c>
-      <c r="C81">
-        <v>1000</v>
-      </c>
-      <c r="D81" t="s">
-        <v>181</v>
-      </c>
-      <c r="E81" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82">
-        <v>4</v>
-      </c>
-      <c r="B82" t="s">
-        <v>183</v>
-      </c>
-      <c r="C82">
-        <v>200</v>
-      </c>
-      <c r="D82" t="s">
-        <v>184</v>
-      </c>
-      <c r="E82" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83">
-        <v>4</v>
-      </c>
-      <c r="B83" t="s">
-        <v>183</v>
-      </c>
-      <c r="C83">
-        <v>400</v>
-      </c>
-      <c r="D83" t="s">
-        <v>186</v>
-      </c>
-      <c r="E83" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84">
-        <v>4</v>
-      </c>
-      <c r="B84" t="s">
-        <v>183</v>
-      </c>
-      <c r="C84">
-        <v>600</v>
-      </c>
-      <c r="D84" t="s">
-        <v>188</v>
-      </c>
-      <c r="E84" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85">
-        <v>4</v>
-      </c>
-      <c r="B85" t="s">
-        <v>183</v>
-      </c>
-      <c r="C85">
-        <v>800</v>
-      </c>
-      <c r="D85" t="s">
-        <v>190</v>
-      </c>
-      <c r="E85" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86">
-        <v>4</v>
-      </c>
-      <c r="B86" t="s">
-        <v>183</v>
-      </c>
-      <c r="C86">
-        <v>1000</v>
-      </c>
-      <c r="D86" t="s">
-        <v>192</v>
-      </c>
-      <c r="E86" t="s">
-        <v>193</v>
-      </c>
-      <c r="F86" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87">
-        <v>4</v>
-      </c>
-      <c r="B87" t="s">
-        <v>194</v>
-      </c>
-      <c r="C87">
-        <v>200</v>
-      </c>
-      <c r="D87" t="s">
-        <v>195</v>
-      </c>
-      <c r="E87" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88">
-        <v>4</v>
-      </c>
-      <c r="B88" t="s">
-        <v>194</v>
-      </c>
-      <c r="C88">
-        <v>400</v>
-      </c>
-      <c r="D88" t="s">
-        <v>197</v>
-      </c>
-      <c r="E88" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89">
-        <v>4</v>
-      </c>
-      <c r="B89" t="s">
-        <v>194</v>
-      </c>
-      <c r="C89">
-        <v>600</v>
-      </c>
-      <c r="D89" t="s">
-        <v>199</v>
-      </c>
-      <c r="E89" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90">
-        <v>4</v>
-      </c>
-      <c r="B90" t="s">
-        <v>194</v>
-      </c>
-      <c r="C90">
-        <v>800</v>
-      </c>
-      <c r="D90" t="s">
-        <v>201</v>
-      </c>
-      <c r="E90" t="s">
-        <v>202</v>
-      </c>
-      <c r="F90" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91">
-        <v>4</v>
-      </c>
-      <c r="B91" t="s">
-        <v>194</v>
-      </c>
-      <c r="C91">
-        <v>1000</v>
-      </c>
-      <c r="D91" t="s">
-        <v>203</v>
-      </c>
-      <c r="E91" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92">
-        <v>4</v>
-      </c>
-      <c r="B92" t="s">
-        <v>205</v>
-      </c>
-      <c r="C92">
-        <v>200</v>
-      </c>
-      <c r="D92" t="s">
-        <v>206</v>
-      </c>
-      <c r="E92" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93">
-        <v>4</v>
-      </c>
-      <c r="B93" t="s">
-        <v>205</v>
-      </c>
-      <c r="C93">
-        <v>400</v>
-      </c>
-      <c r="D93" t="s">
-        <v>208</v>
-      </c>
-      <c r="E93" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94">
-        <v>4</v>
-      </c>
-      <c r="B94" t="s">
-        <v>205</v>
-      </c>
-      <c r="C94">
-        <v>600</v>
-      </c>
-      <c r="D94" t="s">
-        <v>210</v>
-      </c>
-      <c r="E94" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95">
-        <v>4</v>
-      </c>
-      <c r="B95" t="s">
-        <v>205</v>
-      </c>
-      <c r="C95">
-        <v>800</v>
-      </c>
-      <c r="D95" t="s">
-        <v>212</v>
-      </c>
-      <c r="E95" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96">
-        <v>4</v>
-      </c>
-      <c r="B96" t="s">
-        <v>205</v>
-      </c>
-      <c r="C96">
-        <v>1000</v>
-      </c>
-      <c r="D96" t="s">
-        <v>214</v>
-      </c>
-      <c r="E96" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97">
-        <v>4</v>
-      </c>
-      <c r="B97" t="s">
-        <v>216</v>
-      </c>
-      <c r="C97">
-        <v>200</v>
-      </c>
-      <c r="D97" t="s">
-        <v>217</v>
-      </c>
-      <c r="E97" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98">
-        <v>4</v>
-      </c>
-      <c r="B98" t="s">
-        <v>216</v>
-      </c>
-      <c r="C98">
-        <v>400</v>
-      </c>
-      <c r="D98" t="s">
-        <v>219</v>
-      </c>
-      <c r="E98" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99">
-        <v>4</v>
-      </c>
-      <c r="B99" t="s">
-        <v>216</v>
-      </c>
-      <c r="C99">
-        <v>600</v>
-      </c>
-      <c r="D99" t="s">
-        <v>221</v>
-      </c>
-      <c r="E99" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100">
-        <v>4</v>
-      </c>
-      <c r="B100" t="s">
-        <v>216</v>
-      </c>
-      <c r="C100">
-        <v>800</v>
-      </c>
-      <c r="D100" t="s">
-        <v>223</v>
-      </c>
-      <c r="E100" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>4</v>
-      </c>
-      <c r="B101" t="s">
-        <v>216</v>
-      </c>
-      <c r="C101">
-        <v>1000</v>
-      </c>
-      <c r="D101" t="s">
-        <v>225</v>
-      </c>
-      <c r="E101" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>227</v>
-      </c>
-      <c r="B102" t="s">
-        <v>228</v>
-      </c>
-      <c r="D102" t="s">
-        <v>229</v>
-      </c>
-      <c r="E102" t="s">
-        <v>230</v>
       </c>
     </row>
   </sheetData>
